--- a/data/dividends_info_20260518.xlsx
+++ b/data/dividends_info_20260518.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>53.31000137329102</v>
+        <v>52.41999816894531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.168823856089959</v>
+        <v>0.1716902005794381</v>
       </c>
       <c r="J2" t="n">
         <v>301</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.65000152587891</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.280878280796612</v>
+        <v>1.275045501902276</v>
       </c>
       <c r="J3" t="n">
         <v>280</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.399999618530273</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6369426700005446</v>
       </c>
       <c r="J4" t="n">
         <v>210</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>53.31000137329102</v>
+        <v>52.41999816894531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.168823856089959</v>
+        <v>0.1716902005794381</v>
       </c>
       <c r="J6" t="n">
         <v>210</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.996000051498413</v>
+        <v>2.005000114440918</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85771533132955</v>
+        <v>3.840398783292388</v>
       </c>
       <c r="J7" t="n">
         <v>189</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.88500022888184</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>1.130416568610768</v>
+        <v>1.125</v>
       </c>
       <c r="J8" t="n">
         <v>189</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.88500022888184</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>1.130416568610768</v>
+        <v>1.125</v>
       </c>
       <c r="J14" t="n">
         <v>126</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>53.31000137329102</v>
+        <v>52.41999816894531</v>
       </c>
       <c r="I15" t="n">
-        <v>0.168823856089959</v>
+        <v>0.1716902005794381</v>
       </c>
       <c r="J15" t="n">
         <v>126</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.610000133514404</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I16" t="n">
-        <v>6.507592002417079</v>
+        <v>6.637168169600429</v>
       </c>
       <c r="J16" t="n">
         <v>119</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.52299976348877</v>
+        <v>9.616000175476074</v>
       </c>
       <c r="I20" t="n">
-        <v>2.730232137533399</v>
+        <v>2.703826905734512</v>
       </c>
       <c r="J20" t="n">
         <v>63</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15.15999984741211</v>
+        <v>15.23999977111816</v>
       </c>
       <c r="I21" t="n">
-        <v>3.957783680996692</v>
+        <v>3.937007933143675</v>
       </c>
       <c r="J21" t="n">
         <v>63</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.584000110626221</v>
+        <v>3.651999950408936</v>
       </c>
       <c r="I22" t="n">
-        <v>6.138392667670987</v>
+        <v>6.024096467344293</v>
       </c>
       <c r="J22" t="n">
         <v>63</v>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.074999809265137</v>
+        <v>6.034999847412109</v>
       </c>
       <c r="I24" t="n">
-        <v>1.646090586661212</v>
+        <v>1.657000870395736</v>
       </c>
       <c r="J24" t="n">
         <v>63</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3.900000095367432</v>
+        <v>3.914999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>3.076923001682502</v>
+        <v>3.065134129482909</v>
       </c>
       <c r="J26" t="n">
         <v>56</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.399999618530273</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5319149152031317</v>
+        <v>0.5494505264177207</v>
       </c>
       <c r="J27" t="n">
         <v>56</v>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.759999990463257</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I28" t="n">
-        <v>5.434782627474683</v>
+        <v>5.597014785954832</v>
       </c>
       <c r="J28" t="n">
         <v>56</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.220000028610229</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I29" t="n">
-        <v>3.828828779484834</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J29" t="n">
         <v>49</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.190000057220459</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I30" t="n">
-        <v>1.67064436859307</v>
+        <v>1.594533078107776</v>
       </c>
       <c r="J30" t="n">
         <v>49</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30.75</v>
+        <v>30.14999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4975124441056695</v>
       </c>
       <c r="J31" t="n">
         <v>49</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22.55999946594238</v>
+        <v>22.65999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>4.210993007487273</v>
+        <v>4.192409560446202</v>
       </c>
       <c r="J33" t="n">
         <v>35</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>31.70000076293945</v>
+        <v>32</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6151419410310393</v>
+        <v>0.609375</v>
       </c>
       <c r="J34" t="n">
         <v>35</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.865000009536743</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="I35" t="n">
-        <v>1.769436988270957</v>
+        <v>1.727748721293108</v>
       </c>
       <c r="J35" t="n">
         <v>35</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.912000179290771</v>
+        <v>4.967999935150146</v>
       </c>
       <c r="I36" t="n">
-        <v>5.903908579292279</v>
+        <v>5.837359174426708</v>
       </c>
       <c r="J36" t="n">
         <v>35</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.79200005531311</v>
+        <v>3.848000049591064</v>
       </c>
       <c r="I37" t="n">
-        <v>4.219409221152783</v>
+        <v>4.158004104417919</v>
       </c>
       <c r="J37" t="n">
         <v>35</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.628000020980835</v>
+        <v>2.648000001907349</v>
       </c>
       <c r="I38" t="n">
-        <v>5.273972560634571</v>
+        <v>5.234138969039528</v>
       </c>
       <c r="J38" t="n">
         <v>35</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>49.3650016784668</v>
+        <v>49.92499923706055</v>
       </c>
       <c r="I39" t="n">
-        <v>1.27620779616991</v>
+        <v>1.261892858542771</v>
       </c>
       <c r="J39" t="n">
         <v>35</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.09499979019165</v>
+        <v>5.190000057220459</v>
       </c>
       <c r="I40" t="n">
-        <v>2.74779206604705</v>
+        <v>2.697495153304064</v>
       </c>
       <c r="J40" t="n">
         <v>35</v>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.53000068664551</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="I42" t="n">
-        <v>3.465144623753527</v>
+        <v>3.449675410126411</v>
       </c>
       <c r="J42" t="n">
         <v>35</v>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>53.31000137329102</v>
+        <v>52.41999816894531</v>
       </c>
       <c r="I43" t="n">
-        <v>0.168823856089959</v>
+        <v>0.1716902005794381</v>
       </c>
       <c r="J43" t="n">
         <v>35</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.228000164031982</v>
+        <v>6.288000106811523</v>
       </c>
       <c r="I45" t="n">
-        <v>2.911046808364679</v>
+        <v>2.883269671124932</v>
       </c>
       <c r="J45" t="n">
         <v>35</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.270000457763672</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="I46" t="n">
-        <v>3.143893417272044</v>
+        <v>3.066037901358581</v>
       </c>
       <c r="J46" t="n">
         <v>35</v>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.706000328063965</v>
+        <v>9.824000358581543</v>
       </c>
       <c r="I47" t="n">
-        <v>2.853904704691604</v>
+        <v>2.81962530424821</v>
       </c>
       <c r="J47" t="n">
         <v>35</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.160000085830688</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="I49" t="n">
-        <v>3.481012563677942</v>
+        <v>3.395061718401904</v>
       </c>
       <c r="J49" t="n">
         <v>28</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.380000114440918</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I50" t="n">
-        <v>1.00840331285605</v>
+        <v>1.071428566866992</v>
       </c>
       <c r="J50" t="n">
         <v>28</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.069999933242798</v>
+        <v>3.125</v>
       </c>
       <c r="I51" t="n">
-        <v>5.211726497693902</v>
+        <v>5.12</v>
       </c>
       <c r="J51" t="n">
         <v>21</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>27.25</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="I53" t="n">
-        <v>4.073394495412844</v>
+        <v>4.058500857470011</v>
       </c>
       <c r="J53" t="n">
         <v>17</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8849999904632568</v>
+        <v>0.8759999871253967</v>
       </c>
       <c r="I54" t="n">
-        <v>3.389830545003326</v>
+        <v>3.42465758457889</v>
       </c>
       <c r="J54" t="n">
         <v>14</v>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5080000162124634</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I55" t="n">
-        <v>4.527558910624245</v>
+        <v>4.466019541528004</v>
       </c>
       <c r="J55" t="n">
         <v>14</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.400000095367432</v>
+        <v>2.464999914169312</v>
       </c>
       <c r="I58" t="n">
-        <v>7.499999701976788</v>
+        <v>7.302231491584404</v>
       </c>
       <c r="J58" t="n">
         <v>7</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.25</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I59" t="n">
-        <v>3.636363636363636</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J59" t="n">
         <v>7</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13.59000015258789</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="I60" t="n">
-        <v>1.839587911648356</v>
+        <v>1.766784499927548</v>
       </c>
       <c r="J60" t="n">
         <v>7</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.369999885559082</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8902077453638549</v>
+        <v>0.8955224135533352</v>
       </c>
       <c r="J61" t="n">
         <v>7</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I62" t="n">
-        <v>3.75</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J62" t="n">
         <v>7</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.80000019073486</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="I63" t="n">
-        <v>4.202898492634835</v>
+        <v>4.249084367831286</v>
       </c>
       <c r="J63" t="n">
         <v>7</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.183000087738037</v>
+        <v>2.20799994468689</v>
       </c>
       <c r="I64" t="n">
-        <v>4.764085928542579</v>
+        <v>4.710145045531147</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.45499992370605</v>
+        <v>10.78499984741211</v>
       </c>
       <c r="I65" t="n">
-        <v>2.773792464048165</v>
+        <v>2.688919834056245</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.998000025749207</v>
+        <v>2.005000114440918</v>
       </c>
       <c r="I66" t="n">
-        <v>3.853853804187349</v>
+        <v>3.840398783292388</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>37.13999938964844</v>
+        <v>37.56000137329102</v>
       </c>
       <c r="I67" t="n">
-        <v>4.415724359050734</v>
+        <v>4.366347018203803</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>34.27999877929688</v>
+        <v>34.68000030517578</v>
       </c>
       <c r="I68" t="n">
-        <v>5.834305925377931</v>
+        <v>5.767012636679568</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.563999891281128</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="I69" t="n">
-        <v>2.80583622476076</v>
+        <v>2.770083182989831</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>29.73999977111816</v>
+        <v>30.01000022888184</v>
       </c>
       <c r="I70" t="n">
-        <v>0.499193009894291</v>
+        <v>0.4947017623049568</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.03000068664551</v>
+        <v>19.28000068664551</v>
       </c>
       <c r="I71" t="n">
-        <v>4.834471712056318</v>
+        <v>4.77178406242095</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10.39000034332275</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>2.88739162740065</v>
+        <v>2.876318228400512</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>80.01999664306641</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="I73" t="n">
-        <v>1.299675135752601</v>
+        <v>1.266747891996393</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42.81000137329102</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="I74" t="n">
-        <v>1.635131926056716</v>
+        <v>1.62224791482378</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>54.65000152587891</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I75" t="n">
-        <v>4.02561745393221</v>
+        <v>4.00728586312144</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.496999740600586</v>
+        <v>8.631999969482422</v>
       </c>
       <c r="I76" t="n">
-        <v>10.12121956283846</v>
+        <v>9.962928672850376</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.44999980926514</v>
+        <v>11.55399990081787</v>
       </c>
       <c r="I77" t="n">
-        <v>4.890829775794913</v>
+        <v>4.846806342454265</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.140000104904175</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I78" t="n">
-        <v>1.869158786877308</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.649999618530273</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="I79" t="n">
-        <v>3.468208245435428</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.170000076293945</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I80" t="n">
-        <v>4.976958350363231</v>
+        <v>4.886877743701542</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>95.59999847412109</v>
+        <v>94.59999847412109</v>
       </c>
       <c r="I81" t="n">
-        <v>2.154811749874287</v>
+        <v>2.177589887132542</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>14.82999992370605</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="I82" t="n">
-        <v>5.057316276860594</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13.43000030517578</v>
+        <v>13.46000003814697</v>
       </c>
       <c r="I83" t="n">
-        <v>2.233804863611084</v>
+        <v>2.228826145243464</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>34.52000045776367</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="I85" t="n">
-        <v>2.462340639421492</v>
+        <v>2.413401392786865</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>69.30000305175781</v>
+        <v>70.48000335693359</v>
       </c>
       <c r="I86" t="n">
-        <v>1.875901793292959</v>
+        <v>1.844494804315457</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.420000076293945</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="I87" t="n">
-        <v>8.086253286127739</v>
+        <v>8.021390353877555</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.099999904632568</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I88" t="n">
-        <v>7.704918153245615</v>
+        <v>7.460317234453558</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>22.26000022888184</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="I90" t="n">
-        <v>4.492362936737634</v>
+        <v>4.42086632581173</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.630000114440918</v>
+        <v>4.5</v>
       </c>
       <c r="I91" t="n">
-        <v>4.643628394941448</v>
+        <v>4.777777777777778</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>23.88500022888184</v>
+        <v>24</v>
       </c>
       <c r="I92" t="n">
-        <v>1.130416568610768</v>
+        <v>1.125</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.899999618530273</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="I93" t="n">
-        <v>2.020202098045045</v>
+        <v>2.044989830886625</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.494999885559082</v>
+        <v>8.244999885559082</v>
       </c>
       <c r="I94" t="n">
-        <v>2.825191327053265</v>
+        <v>2.910855104077736</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>20.54999923706055</v>
+        <v>20.8799991607666</v>
       </c>
       <c r="I95" t="n">
-        <v>3.844282381165679</v>
+        <v>3.783525056286427</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>34.88000106811523</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="I98" t="n">
-        <v>1.003440336244555</v>
+        <v>0.994318160266916</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.440000057220459</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="I99" t="n">
-        <v>8.607142780666978</v>
+        <v>8.417615744706673</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.220000028610229</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I100" t="n">
-        <v>2.702702667871647</v>
+        <v>2.631578980390385</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>12.75</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="I101" t="n">
-        <v>1.568627450980392</v>
+        <v>1.544401567148357</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>6.820000171661377</v>
+        <v>6.934999942779541</v>
       </c>
       <c r="I102" t="n">
-        <v>1.510263891604988</v>
+        <v>1.485219911317226</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.49399995803833</v>
+        <v>5.592000007629395</v>
       </c>
       <c r="I103" t="n">
-        <v>3.458318191684894</v>
+        <v>3.397711011101131</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>9.765999794006348</v>
+        <v>9.890000343322754</v>
       </c>
       <c r="I104" t="n">
-        <v>4.423510230515567</v>
+        <v>4.368048382239595</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>25.01000022888184</v>
+        <v>25.32999992370605</v>
       </c>
       <c r="I105" t="n">
-        <v>1.759296265387007</v>
+        <v>1.737070672425107</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.789999961853027</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="I107" t="n">
-        <v>6.03337615277985</v>
+        <v>6.103896255094262</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>48.22999954223633</v>
+        <v>49.25</v>
       </c>
       <c r="I108" t="n">
-        <v>2.902757647289591</v>
+        <v>2.842639593908629</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.424999952316284</v>
+        <v>3.5</v>
       </c>
       <c r="I109" t="n">
-        <v>8.759124209537982</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>13</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>0.923076923076923</v>
+        <v>0.9302325856477186</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3.75</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I111" t="n">
-        <v>4.533333333333333</v>
+        <v>4.775280975630273</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>21.89999961853027</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="I112" t="n">
-        <v>3.19634708763971</v>
+        <v>3.325415797486504</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.380000114440918</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I113" t="n">
-        <v>1.47058816458174</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.559999942779541</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="I114" t="n">
-        <v>5.935251859643496</v>
+        <v>5.882352801180245</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8939999938011169</v>
+        <v>0.8980000019073486</v>
       </c>
       <c r="I115" t="n">
-        <v>7.829977682927423</v>
+        <v>7.795100206160386</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>50.5</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I116" t="n">
-        <v>1.405940594059406</v>
+        <v>1.397637816266004</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>95.80000305175781</v>
+        <v>98.94999694824219</v>
       </c>
       <c r="I117" t="n">
-        <v>1.409185758867499</v>
+        <v>1.364325458954936</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>7.079999923706055</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I118" t="n">
-        <v>1.129943515001109</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.578999996185303</v>
+        <v>4.592999935150146</v>
       </c>
       <c r="I120" t="n">
-        <v>3.712601007679067</v>
+        <v>3.701284615725619</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -6103,8 +6103,12 @@
           <t>IT0005568461</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3.832258064516129</v>
+      </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>58.40000152587891</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7705479250725544</v>
+        <v>0.7666098707857425</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -6194,10 +6198,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.059999942779541</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7905138429315346</v>
+        <v>0.8179959323546503</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -6241,10 +6245,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.06000137329102</v>
+        <v>37.04000091552734</v>
       </c>
       <c r="I124" t="n">
-        <v>2.833243284110428</v>
+        <v>2.834773148074722</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -6335,10 +6339,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>20.60000038146973</v>
+        <v>20.5</v>
       </c>
       <c r="I126" t="n">
-        <v>1.844660160015437</v>
+        <v>1.853658536585366</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -6382,10 +6386,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>26.20000076293945</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="I127" t="n">
-        <v>2.290076269191239</v>
+        <v>2.274450413525199</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -6429,10 +6433,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>34.09999847412109</v>
+        <v>36.5</v>
       </c>
       <c r="I128" t="n">
-        <v>1.026393007805028</v>
+        <v>0.9589041095890409</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -6476,10 +6480,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>3.480000019073486</v>
+        <v>3.5</v>
       </c>
       <c r="I129" t="n">
-        <v>0.488505744448992</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -6523,10 +6527,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2.740000009536743</v>
+        <v>2.734999895095825</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3649635023793565</v>
+        <v>0.3656307270040913</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -6570,10 +6574,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21</v>
+        <v>21.03000068664551</v>
       </c>
       <c r="I131" t="n">
-        <v>5.333333333333334</v>
+        <v>5.325724980652158</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6617,10 +6621,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1.440000057220459</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I132" t="n">
-        <v>6.944444168497026</v>
+        <v>6.849314889533817</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -6660,14 +6664,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0003865570</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>7.980000019073486</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="I133" t="n">
-        <v>3.258145355621029</v>
+        <v>10.35856577640916</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6711,10 +6715,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.170000076293945</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="I134" t="n">
-        <v>4.25345607165302</v>
+        <v>4.333333100511447</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -6758,10 +6762,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8.659999847412109</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I135" t="n">
-        <v>4.041570510010938</v>
+        <v>4.013761344978222</v>
       </c>
       <c r="J135" t="n">
         <v>-7</v>
@@ -6805,10 +6809,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4.980000019073486</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I136" t="n">
-        <v>1.927710835990328</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J136" t="n">
         <v>-7</v>
@@ -6946,10 +6950,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.399999618530273</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6369426700005446</v>
       </c>
       <c r="J139" t="n">
         <v>-7</v>
@@ -6993,10 +6997,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18.97999954223633</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="I140" t="n">
-        <v>2.634352012956304</v>
+        <v>2.656748183356812</v>
       </c>
       <c r="J140" t="n">
         <v>-7</v>
@@ -7040,10 +7044,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>2.180000066757202</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I141" t="n">
-        <v>2.752293493699352</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J141" t="n">
         <v>-7</v>
@@ -7087,10 +7091,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.07999992370605</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>3.315649884148807</v>
+        <v>3.259452379572819</v>
       </c>
       <c r="J142" t="n">
         <v>-7</v>
@@ -7134,10 +7138,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.680000066757202</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="I143" t="n">
-        <v>2.71739125505287</v>
+        <v>2.688172022336232</v>
       </c>
       <c r="J143" t="n">
         <v>-7</v>
@@ -7181,10 +7185,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.700000047683716</v>
+        <v>3.759999990463257</v>
       </c>
       <c r="I144" t="n">
-        <v>2.972972934658812</v>
+        <v>2.925531922313842</v>
       </c>
       <c r="J144" t="n">
         <v>-7</v>
@@ -7275,10 +7279,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>4.639999866485596</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="I146" t="n">
-        <v>2.047413852017078</v>
+        <v>1.975051998547481</v>
       </c>
       <c r="J146" t="n">
         <v>-7</v>
@@ -7369,10 +7373,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>7.849999904632568</v>
+        <v>8</v>
       </c>
       <c r="I148" t="n">
-        <v>1.14649682921509</v>
+        <v>1.125</v>
       </c>
       <c r="J148" t="n">
         <v>-7</v>
@@ -7463,10 +7467,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>6.949999809265137</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="I150" t="n">
-        <v>3.16546771277195</v>
+        <v>3.156384600033837</v>
       </c>
       <c r="J150" t="n">
         <v>-7</v>
@@ -7510,10 +7514,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>27.70000076293945</v>
+        <v>27</v>
       </c>
       <c r="I151" t="n">
-        <v>2.202166004327822</v>
+        <v>2.259259259259259</v>
       </c>
       <c r="J151" t="n">
         <v>-14</v>
@@ -7557,10 +7561,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2.819999933242798</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="I152" t="n">
-        <v>5.319149062089187</v>
+        <v>5.281690300468702</v>
       </c>
       <c r="J152" t="n">
         <v>-14</v>
@@ -7604,10 +7608,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.10000038146973</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="I153" t="n">
-        <v>6.306306089579743</v>
+        <v>6.334841519613111</v>
       </c>
       <c r="J153" t="n">
         <v>-14</v>
@@ -7651,10 +7655,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>8.560000419616699</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="I154" t="n">
-        <v>5.963784754380411</v>
+        <v>5.874568753172284</v>
       </c>
       <c r="J154" t="n">
         <v>-14</v>
@@ -7698,10 +7702,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.265000343322754</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="I155" t="n">
-        <v>3.266787523101938</v>
+        <v>3.218116674034246</v>
       </c>
       <c r="J155" t="n">
         <v>-14</v>
@@ -7745,10 +7749,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.784999847412109</v>
+        <v>6.875</v>
       </c>
       <c r="I156" t="n">
-        <v>5.158437846295526</v>
+        <v>5.09090909090909</v>
       </c>
       <c r="J156" t="n">
         <v>-14</v>
@@ -7839,10 +7843,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>16.60000038146973</v>
+        <v>16.85000038146973</v>
       </c>
       <c r="I158" t="n">
-        <v>4.518072185330857</v>
+        <v>4.451038474899915</v>
       </c>
       <c r="J158" t="n">
         <v>-14</v>
@@ -7886,10 +7890,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.35000038146973</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I159" t="n">
-        <v>4.154589218855071</v>
+        <v>4.114832610989668</v>
       </c>
       <c r="J159" t="n">
         <v>-14</v>
@@ -7933,10 +7937,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>4.039999961853027</v>
+        <v>4.15500020980835</v>
       </c>
       <c r="I160" t="n">
-        <v>3.712871322186832</v>
+        <v>3.610108120955276</v>
       </c>
       <c r="J160" t="n">
         <v>-14</v>
@@ -7980,10 +7984,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>11.64000034332275</v>
+        <v>11.68000030517578</v>
       </c>
       <c r="I161" t="n">
-        <v>1.693891702615845</v>
+        <v>1.688090709318117</v>
       </c>
       <c r="J161" t="n">
         <v>-14</v>
@@ -8027,10 +8031,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>27.5</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>3.942652383656005</v>
       </c>
       <c r="J162" t="n">
         <v>-14</v>
@@ -8074,10 +8078,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>68</v>
+        <v>68.09999847412109</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6911764705882353</v>
+        <v>0.6901615426299991</v>
       </c>
       <c r="J163" t="n">
         <v>-14</v>
@@ -8121,10 +8125,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>89.19999694824219</v>
+        <v>90</v>
       </c>
       <c r="I164" t="n">
-        <v>1.345291525846457</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="J164" t="n">
         <v>-14</v>
@@ -8168,10 +8172,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.64999961853027</v>
+        <v>22.45000076293945</v>
       </c>
       <c r="I165" t="n">
-        <v>1.192053000208924</v>
+        <v>1.202672564919094</v>
       </c>
       <c r="J165" t="n">
         <v>-14</v>
@@ -8215,10 +8219,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>10.39999961853027</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I166" t="n">
-        <v>3.653846287868437</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J166" t="n">
         <v>-14</v>
@@ -8262,10 +8266,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>34.20000076293945</v>
+        <v>33.5</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8771929628875695</v>
+        <v>0.8955223880597015</v>
       </c>
       <c r="J167" t="n">
         <v>-14</v>
@@ -8309,10 +8313,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0.1645999997854233</v>
+        <v>0.1671999990940094</v>
       </c>
       <c r="I168" t="n">
-        <v>4.252733905908491</v>
+        <v>4.18660289349894</v>
       </c>
       <c r="J168" t="n">
         <v>-21</v>
@@ -8356,10 +8360,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.78000020980835</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="I169" t="n">
-        <v>2.359881932872724</v>
+        <v>2.335766455876795</v>
       </c>
       <c r="J169" t="n">
         <v>-21</v>
@@ -8403,10 +8407,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2.025000095367432</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="I170" t="n">
-        <v>3.209876392040658</v>
+        <v>3.217821812561921</v>
       </c>
       <c r="J170" t="n">
         <v>-21</v>
@@ -8450,10 +8454,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>8.479999542236328</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I171" t="n">
-        <v>2.948113366690943</v>
+        <v>2.923976542958565</v>
       </c>
       <c r="J171" t="n">
         <v>-21</v>
@@ -8544,10 +8548,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>7.210000038146973</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I173" t="n">
-        <v>6.934812723364478</v>
+        <v>6.944444628409402</v>
       </c>
       <c r="J173" t="n">
         <v>-28</v>
@@ -8591,10 +8595,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>19.27000045776367</v>
+        <v>19.38999938964844</v>
       </c>
       <c r="I174" t="n">
-        <v>3.373118757442074</v>
+        <v>3.352243529966327</v>
       </c>
       <c r="J174" t="n">
         <v>-28</v>
@@ -8638,10 +8642,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>13.01500034332275</v>
+        <v>13.09000015258789</v>
       </c>
       <c r="I175" t="n">
-        <v>4.149058668884653</v>
+        <v>4.125286430139897</v>
       </c>
       <c r="J175" t="n">
         <v>-28</v>
@@ -8685,10 +8689,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>5.323999881744385</v>
+        <v>5.401999950408936</v>
       </c>
       <c r="I176" t="n">
-        <v>1.878287043974078</v>
+        <v>1.851166251721826</v>
       </c>
       <c r="J176" t="n">
         <v>-28</v>
@@ -8732,10 +8736,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>8.039999961853027</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="I177" t="n">
-        <v>1.990049760685867</v>
+        <v>1.980198038499644</v>
       </c>
       <c r="J177" t="n">
         <v>-28</v>
@@ -8779,10 +8783,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>273.7000122070312</v>
+        <v>277</v>
       </c>
       <c r="I178" t="n">
-        <v>1.320789126332064</v>
+        <v>1.305054151624549</v>
       </c>
       <c r="J178" t="n">
         <v>-28</v>
@@ -8826,10 +8830,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>27.89999961853027</v>
+        <v>28</v>
       </c>
       <c r="I179" t="n">
-        <v>4.874552037974697</v>
+        <v>4.857142857142858</v>
       </c>
       <c r="J179" t="n">
         <v>-28</v>
@@ -8873,10 +8877,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>13.91499996185303</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="I180" t="n">
-        <v>41.8368668053144</v>
+        <v>41.85190556334249</v>
       </c>
       <c r="J180" t="n">
         <v>-28</v>
@@ -8920,10 +8924,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>14.21000003814697</v>
+        <v>14.18000030517578</v>
       </c>
       <c r="I181" t="n">
-        <v>4.116819130398016</v>
+        <v>4.125528825175494</v>
       </c>
       <c r="J181" t="n">
         <v>-28</v>
@@ -8967,10 +8971,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>20.46999931335449</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="I182" t="n">
-        <v>3.077674749060652</v>
+        <v>3.024483928504552</v>
       </c>
       <c r="J182" t="n">
         <v>-28</v>
@@ -9014,10 +9018,10 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>149.5500030517578</v>
+        <v>147.9499969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6018054039681422</v>
+        <v>0.608313632013693</v>
       </c>
       <c r="J183" t="n">
         <v>-28</v>
@@ -9061,10 +9065,10 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>70.59999847412109</v>
+        <v>71.45999908447266</v>
       </c>
       <c r="I184" t="n">
-        <v>2.437393820384814</v>
+        <v>2.408060484251962</v>
       </c>
       <c r="J184" t="n">
         <v>-28</v>
@@ -10875,7 +10879,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10885,14 +10889,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10902,14 +10906,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10926,7 +10930,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10977,7 +10981,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10987,14 +10991,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11004,7 +11008,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11049,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11079,7 +11083,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11130,7 +11134,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11140,14 +11144,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11157,7 +11161,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11174,14 +11178,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11198,7 +11202,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11215,7 +11219,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11274,104 +11278,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005425365</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2.759999990463257</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>5.434782627474683</v>
-      </c>
-      <c r="I2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11382,95 +11291,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>